--- a/artfynd/A 17100-2026 artfynd.xlsx
+++ b/artfynd/A 17100-2026 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132523770</v>
+        <v>132523769</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>58332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467730</v>
+        <v>467737</v>
       </c>
       <c r="R2" t="n">
-        <v>7042714</v>
+        <v>7042707</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,21 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -914,50 +904,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132523769</v>
+        <v>132523770</v>
       </c>
       <c r="B4" t="n">
-        <v>58332</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467737</v>
+        <v>467730</v>
       </c>
       <c r="R4" t="n">
-        <v>7042707</v>
+        <v>7042714</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,6 +995,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132523802</v>
+        <v>132523787</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468129</v>
+        <v>467938</v>
       </c>
       <c r="R6" t="n">
-        <v>7042769</v>
+        <v>7042723</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1235,14 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132523787</v>
+        <v>132523802</v>
       </c>
       <c r="B7" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467938</v>
+        <v>468129</v>
       </c>
       <c r="R7" t="n">
-        <v>7042723</v>
+        <v>7042769</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,14 +1352,19 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132523775</v>
+        <v>132523805</v>
       </c>
       <c r="B8" t="n">
-        <v>80439</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467791</v>
+        <v>468120</v>
       </c>
       <c r="R8" t="n">
-        <v>7042742</v>
+        <v>7042799</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>viden</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132523805</v>
+        <v>132523793</v>
       </c>
       <c r="B9" t="n">
         <v>79333</v>
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468120</v>
+        <v>468040</v>
       </c>
       <c r="R9" t="n">
-        <v>7042799</v>
+        <v>7042764</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132523793</v>
+        <v>132523775</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>80439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,21 +1637,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468040</v>
+        <v>467791</v>
       </c>
       <c r="R10" t="n">
-        <v>7042764</v>
+        <v>7042742</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>viden</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132523800</v>
+        <v>132523811</v>
       </c>
       <c r="B13" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468057</v>
+        <v>468066</v>
       </c>
       <c r="R13" t="n">
-        <v>7042717</v>
+        <v>7042878</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,14 +2074,19 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2206,7 +2211,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132523811</v>
+        <v>132523761</v>
       </c>
       <c r="B15" t="n">
         <v>79333</v>
@@ -2237,14 +2242,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468066</v>
+        <v>467698</v>
       </c>
       <c r="R15" t="n">
-        <v>7042878</v>
+        <v>7042731</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2276,7 +2281,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2291,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,21 +2302,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2328,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132523761</v>
+        <v>132523800</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,37 +2329,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467698</v>
+        <v>468057</v>
       </c>
       <c r="R16" t="n">
-        <v>7042731</v>
+        <v>7042717</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2398,7 +2388,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2408,7 +2398,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,6 +2409,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fire killed tree</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2435,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132523782</v>
+        <v>132523759</v>
       </c>
       <c r="B17" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2446,34 +2446,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467941</v>
+        <v>467714</v>
       </c>
       <c r="R17" t="n">
-        <v>7042808</v>
+        <v>7042783</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132523759</v>
+        <v>132523782</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2553,34 +2553,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467714</v>
+        <v>467941</v>
       </c>
       <c r="R18" t="n">
-        <v>7042783</v>
+        <v>7042808</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132523779</v>
+        <v>132523798</v>
       </c>
       <c r="B19" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,21 +2660,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467814</v>
+        <v>468057</v>
       </c>
       <c r="R19" t="n">
-        <v>7042789</v>
+        <v>7042731</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,16 +2740,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Fire killed tree</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2766,10 +2756,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132523798</v>
+        <v>132523779</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,21 +2767,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2791,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468057</v>
+        <v>467814</v>
       </c>
       <c r="R20" t="n">
-        <v>7042731</v>
+        <v>7042789</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2836,7 +2826,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2836,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2857,6 +2847,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fire killed tree</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -4189,10 +4189,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132523764</v>
+        <v>132523814</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>80439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4200,37 +4200,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467690</v>
+        <v>468040</v>
       </c>
       <c r="R32" t="n">
-        <v>7042705</v>
+        <v>7043001</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>viden</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132523785</v>
+        <v>132523764</v>
       </c>
       <c r="B33" t="n">
         <v>79333</v>
@@ -4342,17 +4342,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467885</v>
+        <v>467690</v>
       </c>
       <c r="R33" t="n">
-        <v>7042765</v>
+        <v>7042705</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4402,6 +4402,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4418,7 +4433,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132523809</v>
+        <v>132523785</v>
       </c>
       <c r="B34" t="n">
         <v>79333</v>
@@ -4453,13 +4468,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468084</v>
+        <v>467885</v>
       </c>
       <c r="R34" t="n">
-        <v>7042841</v>
+        <v>7042765</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4488,7 +4503,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4498,7 +4513,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4509,21 +4524,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4540,10 +4540,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132523814</v>
+        <v>132523809</v>
       </c>
       <c r="B35" t="n">
-        <v>80439</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4551,21 +4551,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4575,13 +4575,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>468040</v>
+        <v>468084</v>
       </c>
       <c r="R35" t="n">
-        <v>7043001</v>
+        <v>7042841</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4634,17 +4634,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>viden</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132523760</v>
+        <v>132523794</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>80439</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5140,34 +5140,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467700</v>
+        <v>468042</v>
       </c>
       <c r="R40" t="n">
-        <v>7042749</v>
+        <v>7042771</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5220,6 +5220,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>viden</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5236,10 +5251,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132523794</v>
+        <v>132523760</v>
       </c>
       <c r="B41" t="n">
-        <v>80439</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5247,34 +5262,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468042</v>
+        <v>467700</v>
       </c>
       <c r="R41" t="n">
-        <v>7042771</v>
+        <v>7042749</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5306,7 +5321,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5316,7 +5331,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5327,21 +5342,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>viden</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Salix</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 17100-2026 artfynd.xlsx
+++ b/artfynd/A 17100-2026 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>132523815</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>132523801</v>
       </c>
       <c r="B43" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2026 artfynd.xlsx
+++ b/artfynd/A 17100-2026 artfynd.xlsx
@@ -5361,7 +5361,7 @@
         <v>132523815</v>
       </c>
       <c r="B42" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>132523801</v>
       </c>
       <c r="B43" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 17100-2026 artfynd.xlsx
+++ b/artfynd/A 17100-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132523769</v>
+        <v>132523775</v>
       </c>
       <c r="B2" t="n">
-        <v>58332</v>
+        <v>80489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467737</v>
+        <v>467791</v>
       </c>
       <c r="R2" t="n">
-        <v>7042707</v>
+        <v>7042742</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +766,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>viden</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132523783</v>
+        <v>132523794</v>
       </c>
       <c r="B3" t="n">
-        <v>79090</v>
+        <v>80489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467941</v>
+        <v>468042</v>
       </c>
       <c r="R3" t="n">
-        <v>7042808</v>
+        <v>7042771</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,14 +889,19 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>viden</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132523770</v>
+        <v>132523814</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>80489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467730</v>
+        <v>468040</v>
       </c>
       <c r="R4" t="n">
-        <v>7042714</v>
+        <v>7043001</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,17 +1013,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>viden</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,45 +1041,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132523799</v>
+        <v>132523759</v>
       </c>
       <c r="B5" t="n">
-        <v>79090</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468057</v>
+        <v>467714</v>
       </c>
       <c r="R5" t="n">
-        <v>7042717</v>
+        <v>7042783</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1096,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,16 +1132,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Fire killed tree</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1143,45 +1148,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132523787</v>
+        <v>132523760</v>
       </c>
       <c r="B6" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467938</v>
+        <v>467700</v>
       </c>
       <c r="R6" t="n">
-        <v>7042723</v>
+        <v>7042749</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,16 +1239,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Fire killed tree</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1260,14 +1255,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132523802</v>
+        <v>132523761</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1291,14 +1286,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468129</v>
+        <v>467698</v>
       </c>
       <c r="R7" t="n">
-        <v>7042769</v>
+        <v>7042731</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,21 +1346,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,14 +1362,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132523805</v>
+        <v>132523764</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1413,14 +1393,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468120</v>
+        <v>467690</v>
       </c>
       <c r="R8" t="n">
-        <v>7042799</v>
+        <v>7042705</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1452,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,17 +1456,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1504,14 +1484,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132523793</v>
+        <v>132523770</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1539,13 +1519,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468040</v>
+        <v>467730</v>
       </c>
       <c r="R9" t="n">
-        <v>7042764</v>
+        <v>7042714</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,17 +1578,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1626,45 +1606,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132523775</v>
+        <v>132523772</v>
       </c>
       <c r="B10" t="n">
-        <v>80439</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467791</v>
+        <v>467732</v>
       </c>
       <c r="R10" t="n">
-        <v>7042742</v>
+        <v>7042751</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1696,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,22 +1698,23 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>viden</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,32 +1732,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132523788</v>
+        <v>132523781</v>
       </c>
       <c r="B11" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1783,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467959</v>
+        <v>467940</v>
       </c>
       <c r="R11" t="n">
-        <v>7042718</v>
+        <v>7042830</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1818,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,14 +1824,19 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1865,32 +1854,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132523774</v>
+        <v>132523784</v>
       </c>
       <c r="B12" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1900,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467773</v>
+        <v>467910</v>
       </c>
       <c r="R12" t="n">
-        <v>7042761</v>
+        <v>7042777</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1935,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1945,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,16 +1945,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Fire killed tree</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1982,14 +1961,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132523811</v>
+        <v>132523785</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2017,13 +1996,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468066</v>
+        <v>467885</v>
       </c>
       <c r="R13" t="n">
-        <v>7042878</v>
+        <v>7042765</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,7 +2031,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2041,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,21 +2052,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2104,14 +2068,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132523784</v>
+        <v>132523791</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2139,13 +2103,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467910</v>
+        <v>468009</v>
       </c>
       <c r="R14" t="n">
-        <v>7042777</v>
+        <v>7042752</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2174,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2184,7 +2148,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,6 +2159,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2211,14 +2190,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132523761</v>
+        <v>132523793</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2242,17 +2221,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467698</v>
+        <v>468040</v>
       </c>
       <c r="R15" t="n">
-        <v>7042731</v>
+        <v>7042764</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2281,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2291,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,6 +2281,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2318,32 +2312,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132523800</v>
+        <v>132523798</v>
       </c>
       <c r="B16" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2356,10 +2350,10 @@
         <v>468057</v>
       </c>
       <c r="R16" t="n">
-        <v>7042717</v>
+        <v>7042731</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2388,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,7 +2392,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,16 +2403,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Fire killed tree</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2435,14 +2419,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132523759</v>
+        <v>132523802</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2466,14 +2450,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467714</v>
+        <v>468129</v>
       </c>
       <c r="R17" t="n">
-        <v>7042783</v>
+        <v>7042769</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2505,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,6 +2510,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2542,32 +2541,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132523782</v>
+        <v>132523803</v>
       </c>
       <c r="B18" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2577,10 +2576,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467941</v>
+        <v>468151</v>
       </c>
       <c r="R18" t="n">
-        <v>7042808</v>
+        <v>7042797</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2612,7 +2611,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2622,7 +2621,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,6 +2632,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2649,14 +2663,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132523798</v>
+        <v>132523805</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2684,10 +2698,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468057</v>
+        <v>468120</v>
       </c>
       <c r="R19" t="n">
-        <v>7042731</v>
+        <v>7042799</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2719,7 +2733,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2743,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,6 +2754,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2756,32 +2785,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132523779</v>
+        <v>132523809</v>
       </c>
       <c r="B20" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2791,10 +2820,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467814</v>
+        <v>468084</v>
       </c>
       <c r="R20" t="n">
-        <v>7042789</v>
+        <v>7042841</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2826,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2836,7 +2865,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,14 +2877,19 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2873,32 +2907,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132523776</v>
+        <v>132523811</v>
       </c>
       <c r="B21" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2908,10 +2942,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467791</v>
+        <v>468066</v>
       </c>
       <c r="R21" t="n">
-        <v>7042742</v>
+        <v>7042878</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2943,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2953,7 +2987,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2967,17 +3001,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>viden</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2995,32 +3029,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132523778</v>
+        <v>132523817</v>
       </c>
       <c r="B22" t="n">
-        <v>79090</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3030,10 +3064,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467815</v>
+        <v>468052</v>
       </c>
       <c r="R22" t="n">
-        <v>7042787</v>
+        <v>7042965</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3065,7 +3099,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3075,7 +3109,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,14 +3121,19 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3112,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132523768</v>
+        <v>132523773</v>
       </c>
       <c r="B23" t="n">
-        <v>80438</v>
+        <v>79130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,34 +3162,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467721</v>
+        <v>467774</v>
       </c>
       <c r="R23" t="n">
-        <v>7042694</v>
+        <v>7042761</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3182,7 +3221,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3192,7 +3231,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3204,19 +3243,14 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>viden</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix</t>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3234,10 +3268,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132523790</v>
+        <v>132523778</v>
       </c>
       <c r="B24" t="n">
-        <v>79090</v>
+        <v>79130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,10 +3303,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467996</v>
+        <v>467815</v>
       </c>
       <c r="R24" t="n">
-        <v>7042703</v>
+        <v>7042787</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3304,7 +3338,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3314,7 +3348,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3351,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132523803</v>
+        <v>132523783</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>79130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3362,21 +3396,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3386,13 +3420,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468151</v>
+        <v>467941</v>
       </c>
       <c r="R25" t="n">
-        <v>7042797</v>
+        <v>7042808</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3421,7 +3455,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3431,7 +3465,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,19 +3477,14 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3473,10 +3502,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132523817</v>
+        <v>132523786</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>79130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,21 +3513,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3508,10 +3537,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468052</v>
+        <v>467936</v>
       </c>
       <c r="R26" t="n">
-        <v>7042965</v>
+        <v>7042721</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3543,7 +3572,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3553,7 +3582,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3565,19 +3594,14 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3595,10 +3619,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132523772</v>
+        <v>132523790</v>
       </c>
       <c r="B27" t="n">
-        <v>79333</v>
+        <v>79130</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3606,37 +3630,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467732</v>
+        <v>467996</v>
       </c>
       <c r="R27" t="n">
-        <v>7042751</v>
+        <v>7042703</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3668,7 +3689,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3678,7 +3699,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3687,23 +3708,17 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3721,10 +3736,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132523781</v>
+        <v>132523799</v>
       </c>
       <c r="B28" t="n">
-        <v>79333</v>
+        <v>79130</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3732,21 +3747,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3756,10 +3771,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467940</v>
+        <v>468057</v>
       </c>
       <c r="R28" t="n">
-        <v>7042830</v>
+        <v>7042717</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3791,7 +3806,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,7 +3816,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,19 +3828,14 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3843,10 +3853,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132523791</v>
+        <v>132523768</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>80488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3854,37 +3864,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468009</v>
+        <v>467721</v>
       </c>
       <c r="R29" t="n">
-        <v>7042752</v>
+        <v>7042694</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3913,7 +3923,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3923,7 +3933,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3937,17 +3947,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>viden</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3965,10 +3975,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132523789</v>
+        <v>132523776</v>
       </c>
       <c r="B30" t="n">
-        <v>79091</v>
+        <v>80488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3976,21 +3986,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4000,10 +4010,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467996</v>
+        <v>467791</v>
       </c>
       <c r="R30" t="n">
-        <v>7042703</v>
+        <v>7042742</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4035,7 +4045,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4045,7 +4055,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4057,14 +4067,19 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>viden</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Salix</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4082,45 +4097,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132523813</v>
+        <v>132523767</v>
       </c>
       <c r="B31" t="n">
-        <v>79091</v>
+        <v>80493</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468020</v>
+        <v>467721</v>
       </c>
       <c r="R31" t="n">
-        <v>7042921</v>
+        <v>7042694</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4152,7 +4167,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4162,7 +4177,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4173,6 +4188,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>viden</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4189,10 +4219,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132523814</v>
+        <v>132523801</v>
       </c>
       <c r="B32" t="n">
-        <v>80439</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4200,37 +4230,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468040</v>
+        <v>468068</v>
       </c>
       <c r="R32" t="n">
-        <v>7043001</v>
+        <v>7042726</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4259,7 +4294,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4269,7 +4304,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4283,17 +4323,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>viden</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4311,10 +4351,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132523764</v>
+        <v>132523815</v>
       </c>
       <c r="B33" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4322,34 +4362,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467690</v>
+        <v>468056</v>
       </c>
       <c r="R33" t="n">
-        <v>7042705</v>
+        <v>7042997</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4381,7 +4426,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4391,7 +4436,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4405,17 +4455,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4433,48 +4483,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132523785</v>
+        <v>132523769</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>58349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långloken, Jmt</t>
+          <t>långloken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467885</v>
+        <v>467737</v>
       </c>
       <c r="R34" t="n">
-        <v>7042765</v>
+        <v>7042707</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4503,7 +4558,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4513,7 +4568,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4540,45 +4595,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132523809</v>
+        <v>132523795</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>58131</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103023</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>468084</v>
+        <v>468041</v>
       </c>
       <c r="R35" t="n">
-        <v>7042841</v>
+        <v>7042773</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4610,7 +4670,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4620,7 +4680,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4631,21 +4691,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4662,45 +4707,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132523773</v>
+        <v>132523796</v>
       </c>
       <c r="B36" t="n">
-        <v>79090</v>
+        <v>99195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467774</v>
+        <v>468048</v>
       </c>
       <c r="R36" t="n">
-        <v>7042761</v>
+        <v>7042769</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4732,7 +4781,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4742,7 +4791,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4753,16 +4802,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Fire killed tree</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4779,45 +4818,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132523767</v>
+        <v>132523774</v>
       </c>
       <c r="B37" t="n">
-        <v>80467</v>
+        <v>79131</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467721</v>
+        <v>467773</v>
       </c>
       <c r="R37" t="n">
-        <v>7042694</v>
+        <v>7042761</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4849,7 +4888,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4859,7 +4898,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4871,19 +4910,14 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>viden</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix</t>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4901,10 +4935,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132523786</v>
+        <v>132523779</v>
       </c>
       <c r="B38" t="n">
-        <v>79090</v>
+        <v>79131</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4912,21 +4946,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4936,10 +4970,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467936</v>
+        <v>467814</v>
       </c>
       <c r="R38" t="n">
-        <v>7042721</v>
+        <v>7042789</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4971,7 +5005,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4981,7 +5015,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5018,49 +5052,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132523796</v>
+        <v>132523782</v>
       </c>
       <c r="B39" t="n">
-        <v>99130</v>
+        <v>79131</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468048</v>
+        <v>467941</v>
       </c>
       <c r="R39" t="n">
-        <v>7042769</v>
+        <v>7042808</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5092,7 +5122,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5102,7 +5132,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5129,10 +5159,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132523794</v>
+        <v>132523787</v>
       </c>
       <c r="B40" t="n">
-        <v>80439</v>
+        <v>79131</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5140,21 +5170,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5164,10 +5194,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468042</v>
+        <v>467938</v>
       </c>
       <c r="R40" t="n">
-        <v>7042771</v>
+        <v>7042723</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5199,7 +5229,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5209,7 +5239,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5221,19 +5251,14 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>viden</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix</t>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Salix</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5251,10 +5276,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132523760</v>
+        <v>132523788</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>79131</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5262,34 +5287,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>långloken, Jmt</t>
+          <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467700</v>
+        <v>467959</v>
       </c>
       <c r="R41" t="n">
-        <v>7042749</v>
+        <v>7042718</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5321,7 +5346,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5331,7 +5356,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5342,6 +5367,16 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Fire killed tree</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5358,10 +5393,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132523815</v>
+        <v>132523789</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>79131</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5369,39 +5404,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468056</v>
+        <v>467996</v>
       </c>
       <c r="R42" t="n">
-        <v>7042997</v>
+        <v>7042703</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5433,7 +5463,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5443,12 +5473,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5460,19 +5485,14 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5490,10 +5510,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132523801</v>
+        <v>132523800</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>79131</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5501,42 +5521,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långloken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468068</v>
+        <v>468057</v>
       </c>
       <c r="R43" t="n">
-        <v>7042726</v>
+        <v>7042717</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5565,7 +5580,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5575,12 +5590,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5592,19 +5602,14 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5619,6 +5624,113 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132523813</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långloken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>468020</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7042921</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17100-2026 artfynd.xlsx
+++ b/artfynd/A 17100-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523775</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523794</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523814</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523759</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523760</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523761</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523764</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1603,6 +1643,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523770</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1729,6 +1774,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523772</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1851,6 +1901,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523781</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1958,6 +2013,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523784</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2065,6 +2125,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523785</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2187,6 +2252,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523791</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2309,6 +2379,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523793</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2416,6 +2491,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523798</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2538,6 +2618,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523802</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2660,6 +2745,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523803</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2782,6 +2872,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523805</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2904,6 +2999,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523809</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3026,6 +3126,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523811</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3148,6 +3253,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523817</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3265,6 +3375,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523773</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3382,6 +3497,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523778</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3499,6 +3619,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523783</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3616,6 +3741,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523786</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3733,6 +3863,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523790</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3850,6 +3985,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523799</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3972,6 +4112,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523768</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4094,6 +4239,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523776</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4216,6 +4366,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523767</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4348,6 +4503,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523801</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4480,6 +4640,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523815</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4592,6 +4757,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523769</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4704,6 +4874,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523795</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4815,6 +4990,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523796</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4932,6 +5112,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523774</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5049,6 +5234,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523779</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5156,6 +5346,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523782</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5273,6 +5468,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523787</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5390,6 +5590,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523788</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5507,6 +5712,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523789</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5624,6 +5834,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523800</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5731,8 +5946,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132523813</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>